--- a/Results/ThesisExperimentList.xlsx
+++ b/Results/ThesisExperimentList.xlsx
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\MS_BSU\SLFA_Julia\ThesisExperiments\BradenKingThesis\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB182282-1F47-4AE2-A56F-74E5373538A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A25383-BAB9-4C08-BC5E-C31844334BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57600" yWindow="12150" windowWidth="15705" windowHeight="15600" activeTab="1" xr2:uid="{C4202BFB-F5A2-4916-9270-58B282AAFCCC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" firstSheet="1" activeTab="2" xr2:uid="{C4202BFB-F5A2-4916-9270-58B282AAFCCC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="TimeResults" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId7"/>
+    <pivotCache cacheId="15" r:id="rId8"/>
+    <pivotCache cacheId="21" r:id="rId9"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="69">
   <si>
     <t>1D Shape</t>
   </si>
@@ -149,15 +158,115 @@
   <si>
     <t>Something Wrong Here</t>
   </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Solver</t>
+  </si>
+  <si>
+    <t>clean</t>
+  </si>
+  <si>
+    <t>LSQ</t>
+  </si>
+  <si>
+    <t>CG</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>IG</t>
+  </si>
+  <si>
+    <t>noisy</t>
+  </si>
+  <si>
+    <t>AsymmetricRBF</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Sine</t>
+  </si>
+  <si>
+    <t>Composite Sine</t>
+  </si>
+  <si>
+    <t>Sin E</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Average of Time</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RMSE </t>
+  </si>
+  <si>
+    <t>Max Error</t>
+  </si>
+  <si>
+    <t>Bound Error</t>
+  </si>
+  <si>
+    <t>Noisy</t>
+  </si>
+  <si>
+    <t>Clean/Noisy</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average of RMSE </t>
+  </si>
+  <si>
+    <t>Average of Max Error</t>
+  </si>
+  <si>
+    <t>Average of Bound Error</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,16 +291,42 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor theme="6" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -199,11 +334,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -215,12 +399,427 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="37">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="15" formatCode="0.00E+00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -239,9 +838,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -276,7 +872,7 @@
         <xdr:cNvPr id="2" name="Content Placeholder 14" descr="A graph with numbers and symbols&#10;&#10;AI-generated content may be incorrect.">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC6E1903-3476-3E12-D4E9-E540521F69D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -319,9 +915,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>13</xdr:col>
-          <xdr:colOff>447675</xdr:colOff>
+          <xdr:colOff>450850</xdr:colOff>
           <xdr:row>16</xdr:row>
-          <xdr:rowOff>28575</xdr:rowOff>
+          <xdr:rowOff>31750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -331,7 +927,7 @@
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E9112BA-C2F0-9EB7-94B0-AAB8F0E1D5CB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -352,23 +948,10 @@
               <a:solidFill>
                 <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:miter lim="800000"/>
               <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
+              <a:tailEnd/>
             </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -379,8 +962,1524 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Braden" refreshedDate="46216.167976620367" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{7739753F-D0A8-49BF-82D7-16FBFCAD70CE}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G61" sheet="TimeResults"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Problem" numFmtId="0">
+      <sharedItems count="5">
+        <s v="AsymmetricRBF"/>
+        <s v="Composite Sine"/>
+        <s v="Sin E"/>
+        <s v="Sine"/>
+        <s v="Step"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Data Type" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Solver" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Time" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8042199999999997E-2" maxValue="70.881799999999998"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Braden" refreshedDate="46216.168284375002" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{ED65F6BD-5FDD-40DC-BE08-FDCF63EBA867}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G61" sheet="TimeResults"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="Problem" numFmtId="0">
+      <sharedItems count="5">
+        <s v="AsymmetricRBF"/>
+        <s v="Composite Sine"/>
+        <s v="Sin E"/>
+        <s v="Sine"/>
+        <s v="Step"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Data Type" numFmtId="0">
+      <sharedItems count="2">
+        <s v="clean"/>
+        <s v="noisy"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Solver" numFmtId="0">
+      <sharedItems count="5">
+        <s v="CG"/>
+        <s v="GD"/>
+        <s v="IG"/>
+        <s v="LBFGS"/>
+        <s v="LSQ"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Time" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8042199999999997E-2" maxValue="70.881799999999998"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Braden" refreshedDate="46216.254153009257" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="60" xr:uid="{77065337-E71E-4C1F-852F-A31D2F5498FD}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table3"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Problem" numFmtId="0">
+      <sharedItems count="5">
+        <s v="AsymmetricRBF"/>
+        <s v="Composite Sine"/>
+        <s v="Sin E"/>
+        <s v="Sine"/>
+        <s v="Step"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Data Type" numFmtId="0">
+      <sharedItems count="2">
+        <s v="clean"/>
+        <s v="noisy"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Solver" numFmtId="0">
+      <sharedItems count="6">
+        <s v="CG"/>
+        <s v="GD"/>
+        <s v="IG"/>
+        <s v="LBFGS"/>
+        <s v="LSQ"/>
+        <s v="NM"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Time" numFmtId="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8042199999999997E-2" maxValue="70.881799999999998"/>
+    </cacheField>
+    <cacheField name="RMSE " numFmtId="11">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.4497472269780495E-5" maxValue="2.4102050946459301"/>
+    </cacheField>
+    <cacheField name="Max Error" numFmtId="11">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.5131480007299601E-4" maxValue="5.2920800991820203"/>
+    </cacheField>
+    <cacheField name="Bound Error" numFmtId="11">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="4.22915047950317E-4" maxValue="7.7159285101947397"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <x v="0"/>
+    <s v="clean"/>
+    <s v="CG"/>
+    <n v="70.881799999999998"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="noisy"/>
+    <s v="CG"/>
+    <n v="16.0017"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="clean"/>
+    <s v="GD"/>
+    <n v="61.017899999999997"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="noisy"/>
+    <s v="GD"/>
+    <n v="17.398199999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="clean"/>
+    <s v="IG"/>
+    <n v="0.272123"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="noisy"/>
+    <s v="IG"/>
+    <n v="7.5115100000000004E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="noisy"/>
+    <s v="LBFGS"/>
+    <n v="5.0377299999999998"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="clean"/>
+    <s v="LBFGS"/>
+    <n v="13.916399999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="clean"/>
+    <s v="LSQ"/>
+    <n v="12.635400000000001"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <s v="noisy"/>
+    <s v="LSQ"/>
+    <n v="3.9053200000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="clean"/>
+    <s v="CG"/>
+    <n v="36.898899999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="noisy"/>
+    <s v="CG"/>
+    <n v="7.8173300000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="clean"/>
+    <s v="GD"/>
+    <n v="47.877200000000002"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="noisy"/>
+    <s v="GD"/>
+    <n v="7.7334100000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="clean"/>
+    <s v="IG"/>
+    <n v="0.26216699999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="noisy"/>
+    <s v="IG"/>
+    <n v="0.326992"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="noisy"/>
+    <s v="LBFGS"/>
+    <n v="2.6439900000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="clean"/>
+    <s v="LBFGS"/>
+    <n v="1.80654"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="clean"/>
+    <s v="LSQ"/>
+    <n v="2.7180300000000002"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="noisy"/>
+    <s v="LSQ"/>
+    <n v="0.98388299999999995"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="clean"/>
+    <s v="CG"/>
+    <n v="62.610999999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="noisy"/>
+    <s v="CG"/>
+    <n v="8.5870700000000006"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="clean"/>
+    <s v="CG"/>
+    <n v="62.610999999999997"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="noisy"/>
+    <s v="CG"/>
+    <n v="8.5870700000000006"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="clean"/>
+    <s v="GD"/>
+    <n v="54.771299999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="noisy"/>
+    <s v="GD"/>
+    <n v="14.228300000000001"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="clean"/>
+    <s v="GD"/>
+    <n v="54.771299999999997"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="noisy"/>
+    <s v="GD"/>
+    <n v="14.228300000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="clean"/>
+    <s v="IG"/>
+    <n v="0.34911399999999998"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="noisy"/>
+    <s v="IG"/>
+    <n v="7.0940500000000004E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="clean"/>
+    <s v="IG"/>
+    <n v="0.34911399999999998"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="noisy"/>
+    <s v="IG"/>
+    <n v="7.0940500000000004E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="noisy"/>
+    <s v="LBFGS"/>
+    <n v="1.6848399999999999"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="clean"/>
+    <s v="LBFGS"/>
+    <n v="2.87683"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="noisy"/>
+    <s v="LBFGS"/>
+    <n v="1.6848399999999999"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="clean"/>
+    <s v="LBFGS"/>
+    <n v="2.87683"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="clean"/>
+    <s v="LSQ"/>
+    <n v="4.4576900000000004"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="noisy"/>
+    <s v="LSQ"/>
+    <n v="1.5675600000000001"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="clean"/>
+    <s v="LSQ"/>
+    <n v="4.4576900000000004"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="noisy"/>
+    <s v="LSQ"/>
+    <n v="1.5675600000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="clean"/>
+    <s v="CG"/>
+    <n v="6.6156800000000002"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="noisy"/>
+    <s v="CG"/>
+    <n v="9.6140600000000003"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="clean"/>
+    <s v="GD"/>
+    <n v="35.988700000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="noisy"/>
+    <s v="GD"/>
+    <n v="17.239699999999999"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="clean"/>
+    <s v="IG"/>
+    <n v="0.292354"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="noisy"/>
+    <s v="IG"/>
+    <n v="6.8042199999999997E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="noisy"/>
+    <s v="LBFGS"/>
+    <n v="3.1019899999999998"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="clean"/>
+    <s v="LBFGS"/>
+    <n v="13.1905"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="clean"/>
+    <s v="LSQ"/>
+    <n v="1.1140000000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="noisy"/>
+    <s v="LSQ"/>
+    <n v="2.7850799999999998"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="70.881799999999998"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="16.0017"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="61.017899999999997"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="17.398199999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.272123"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="7.5115100000000004E-2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="5.0377299999999998"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="13.916399999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="12.635400000000001"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="3.9053200000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="36.898899999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7.8173300000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47.877200000000002"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="7.7334100000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.26216699999999998"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="0.326992"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="2.6439900000000001"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="1.80654"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="2.7180300000000002"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="0.98388299999999995"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="62.610999999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8.5870700000000006"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="62.610999999999997"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8.5870700000000006"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="54.771299999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="14.228300000000001"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="54.771299999999997"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="14.228300000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.34911399999999998"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="7.0940500000000004E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.34911399999999998"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="7.0940500000000004E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1.6848399999999999"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2.87683"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1.6848399999999999"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2.87683"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4.4576900000000004"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="1.5675600000000001"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4.4576900000000004"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="1.5675600000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="6.6156800000000002"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9.6140600000000003"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="35.988700000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="17.239699999999999"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.292354"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6.8042199999999997E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="3.1019899999999998"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="13.1905"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1.1140000000000001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="2.7850799999999998"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="60">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="70.881799999999998"/>
+    <n v="8.0158078411725396E-5"/>
+    <n v="3.0149357368290598E-4"/>
+    <n v="5.63382571350472E-4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="61.017899999999997"/>
+    <n v="1.0708893831739E-4"/>
+    <n v="2.5131480007299601E-4"/>
+    <n v="4.22915047950317E-4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.272123"/>
+    <n v="5.5376499405338701E-4"/>
+    <n v="1.5675444224314201E-3"/>
+    <n v="2.7592100881690998E-3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="13.916399999999999"/>
+    <n v="7.4497472269780495E-5"/>
+    <n v="3.65258340649205E-4"/>
+    <n v="4.7883756930836501E-4"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="12.635400000000001"/>
+    <n v="1.82414863568795E-4"/>
+    <n v="9.4711775251927197E-4"/>
+    <n v="1.22394752256336E-3"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1.9495819000000001"/>
+    <n v="0.250117713343676"/>
+    <n v="1.5741567529357801"/>
+    <n v="2.8632267143095902"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="16.0017"/>
+    <n v="5.0852103951725701E-2"/>
+    <n v="0.34232484116550099"/>
+    <n v="0.67448009802876696"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="17.398199999999999"/>
+    <n v="0.61338183564672499"/>
+    <n v="2.9628652746893702"/>
+    <n v="4.2693759980444002"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="7.5115100000000004E-2"/>
+    <n v="0.23048247046100401"/>
+    <n v="1.5515994839971401"/>
+    <n v="2.9870621343039798"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="5.0377299999999998"/>
+    <n v="6.2147256965994498E-2"/>
+    <n v="0.75542110204059698"/>
+    <n v="1.3574724764266599"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="3.9053200000000001"/>
+    <n v="6.6219476715996706E-2"/>
+    <n v="0.41891422090307801"/>
+    <n v="0.809559330529667"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="0.54042769999999996"/>
+    <n v="0.217587732167494"/>
+    <n v="1.40379689424623"/>
+    <n v="2.72814040764188"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="36.898899999999998"/>
+    <n v="2.5091416902881399E-3"/>
+    <n v="7.2222514734408497E-3"/>
+    <n v="1.4113510787013899E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="47.877200000000002"/>
+    <n v="5.5010172994750901E-3"/>
+    <n v="1.6524525225234801E-2"/>
+    <n v="2.7843177139354601E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.26216699999999998"/>
+    <n v="6.6681803044133896E-3"/>
+    <n v="2.0590593675692499E-2"/>
+    <n v="2.3637880091791501E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="1.80654"/>
+    <n v="2.6246408285867402E-3"/>
+    <n v="7.3498517231258102E-3"/>
+    <n v="1.4359291311023901E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="2.7180300000000002"/>
+    <n v="2.6246393560013302E-3"/>
+    <n v="7.3498541312440697E-3"/>
+    <n v="1.4359288182437299E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="4.3649449000000002"/>
+    <n v="3.01868263179329E-3"/>
+    <n v="9.0967723677438505E-3"/>
+    <n v="1.7050883086645801E-2"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="7.8173300000000001"/>
+    <n v="0.801291367502725"/>
+    <n v="2.88919091353198"/>
+    <n v="5.37246542255048"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="7.7334100000000001"/>
+    <n v="0.96598603616919898"/>
+    <n v="3.5582416127633998"/>
+    <n v="6.28696568810778"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="0.326992"/>
+    <n v="2.4102050946459301"/>
+    <n v="5.2920800991820203"/>
+    <n v="6.77487680978372"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="2.6439900000000001"/>
+    <n v="0.77456738695982197"/>
+    <n v="2.88986608068537"/>
+    <n v="5.3199692641874696"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="0.98388299999999995"/>
+    <n v="0.65760417888491196"/>
+    <n v="2.4889104970683902"/>
+    <n v="4.9520824509459498"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="2.1352106000000002"/>
+    <n v="1.3240908227252699"/>
+    <n v="4.4642172980045904"/>
+    <n v="7.7159285101947397"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="62.610999999999997"/>
+    <n v="2.3646261766681201E-3"/>
+    <n v="7.6746499836514602E-3"/>
+    <n v="1.2810808666554801E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="54.771299999999997"/>
+    <n v="1.1550009147432601E-3"/>
+    <n v="3.2988905937129001E-3"/>
+    <n v="6.5095841618804896E-3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.34911399999999998"/>
+    <n v="6.9063927253939996E-4"/>
+    <n v="2.3405484709488802E-3"/>
+    <n v="3.9843163903979101E-3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2.87683"/>
+    <n v="2.1818662183589101E-3"/>
+    <n v="7.8308685916167308E-3"/>
+    <n v="1.2375491780561699E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="4.4576900000000004"/>
+    <n v="1.9557646257379298E-3"/>
+    <n v="6.7816752973434303E-3"/>
+    <n v="1.12395882886645E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="4.0496929000000002"/>
+    <n v="1.93825715071022E-3"/>
+    <n v="6.4403342578306603E-3"/>
+    <n v="1.1390192968623499E-2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="8.5870700000000006"/>
+    <n v="4.1453415836221599E-2"/>
+    <n v="0.14040456794717501"/>
+    <n v="0.245064119550231"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="14.228300000000001"/>
+    <n v="0.13904915029484899"/>
+    <n v="0.386911454156115"/>
+    <n v="0.68318059147913801"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="7.0940500000000004E-2"/>
+    <n v="0.15612056582273201"/>
+    <n v="0.51286766610365897"/>
+    <n v="0.71278513265916699"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1.6848399999999999"/>
+    <n v="4.1456865722321698E-2"/>
+    <n v="0.140393759291254"/>
+    <n v="0.24506370248391099"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="1.5675600000000001"/>
+    <n v="4.0833320272044303E-2"/>
+    <n v="0.140925650846046"/>
+    <n v="0.24505734285731401"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="1.2574320000000001"/>
+    <n v="4.0787048159407598E-2"/>
+    <n v="0.14148670760075799"/>
+    <n v="0.245053054690517"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="54.652799999999999"/>
+    <n v="4.4510542736962699E-3"/>
+    <n v="1.6507426046054201E-2"/>
+    <n v="2.6229440676767898E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="63.719700000000003"/>
+    <n v="6.3331295728659403E-3"/>
+    <n v="1.7931398656809299E-2"/>
+    <n v="3.3279032323531001E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.33784500000000001"/>
+    <n v="1.8309538424324302E-2"/>
+    <n v="8.5810910075569402E-2"/>
+    <n v="8.5895394944806996E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="2.5577700000000001"/>
+    <n v="4.0142921929919003E-3"/>
+    <n v="1.28594873147887E-2"/>
+    <n v="2.28128592064397E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="3.11145"/>
+    <n v="4.0142916824074297E-3"/>
+    <n v="1.28594959878779E-2"/>
+    <n v="2.28128717828079E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="4.5974335000000002"/>
+    <n v="5.5891524503640499E-3"/>
+    <n v="2.2443603715458799E-2"/>
+    <n v="3.4773400574761498E-2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="6.6707299999999998"/>
+    <n v="0.24360513166502101"/>
+    <n v="0.75915050824021502"/>
+    <n v="1.51023010747413"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="13.828099999999999"/>
+    <n v="0.45993125581394501"/>
+    <n v="1.88492546748256"/>
+    <n v="3.0087160259682402"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="8.8483400000000004E-2"/>
+    <n v="0.50439958268898499"/>
+    <n v="1.17428808388124"/>
+    <n v="1.8642873922166101"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="1.0792299999999999"/>
+    <n v="0.23694535093489999"/>
+    <n v="0.75638934371671995"/>
+    <n v="1.51030932819276"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="1.5731599999999999"/>
+    <n v="0.229718036094717"/>
+    <n v="0.77961498364586002"/>
+    <n v="1.4616668194278799"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="1.5713614"/>
+    <n v="0.40071241252664902"/>
+    <n v="0.96581405788355201"/>
+    <n v="1.9214747959175"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="6.6156800000000002"/>
+    <n v="0.14592883124204001"/>
+    <n v="0.60449260703643604"/>
+    <n v="1.0055006730877001"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="35.988700000000001"/>
+    <n v="0.12968113651434601"/>
+    <n v="0.57749149831848201"/>
+    <n v="1.0185314034547699"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="0.292354"/>
+    <n v="0.31220361801305802"/>
+    <n v="0.73540788758055997"/>
+    <n v="0.73616458940486895"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="13.1905"/>
+    <n v="3.3790369124594198E-3"/>
+    <n v="1.0685154303572E-2"/>
+    <n v="1.9292474326642099E-2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="4"/>
+    <n v="1.1140000000000001"/>
+    <n v="0.249127964789603"/>
+    <n v="0.88938504322949796"/>
+    <n v="1.3298393318872299"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="5"/>
+    <n v="1.9451883000000001"/>
+    <n v="0.40359911336578402"/>
+    <n v="0.62498700848665001"/>
+    <n v="1.1677899083337999"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="9.6140600000000003"/>
+    <n v="9.8471561707902805E-2"/>
+    <n v="0.33753961371707603"/>
+    <n v="0.61523698654407699"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="17.239699999999999"/>
+    <n v="0.14224438082638899"/>
+    <n v="0.414745195132116"/>
+    <n v="0.80134390579414105"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="6.8042199999999997E-2"/>
+    <n v="0.50760907712574199"/>
+    <n v="1.09124651945925"/>
+    <n v="1.10549516064681"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <n v="3.1019899999999998"/>
+    <n v="9.8036203584847603E-2"/>
+    <n v="0.30778567176863803"/>
+    <n v="0.58570046607555803"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="2.7850799999999998"/>
+    <n v="9.71806155299062E-2"/>
+    <n v="0.295448031130705"/>
+    <n v="0.57115690156416798"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="5"/>
+    <n v="0.69017720000000005"/>
+    <n v="0.131432654739953"/>
+    <n v="0.54299357139798299"/>
+    <n v="1.0098621954920799"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EDC6318-5478-44BB-84A3-F944FE4F7B2F}" name="PivotTable7" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K65:O72" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisPage" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+    <pivotField dataField="1" numFmtId="11" showAll="0"/>
+    <pivotField dataField="1" numFmtId="11" showAll="0"/>
+    <pivotField dataField="1" numFmtId="11" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="1" hier="-1"/>
+    <pageField fld="0" hier="-1"/>
+  </pageFields>
+  <dataFields count="4">
+    <dataField name="Average of Time" fld="3" subtotal="average" baseField="2" baseItem="0" numFmtId="2"/>
+    <dataField name="Average of RMSE " fld="4" subtotal="average" baseField="2" baseItem="0" numFmtId="11"/>
+    <dataField name="Average of Max Error" fld="5" subtotal="average" baseField="2" baseItem="0" numFmtId="11"/>
+    <dataField name="Average of Bound Error" fld="6" subtotal="average" baseField="2" baseItem="0" numFmtId="11"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="21">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="3" selected="0">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0B6588A0-F12E-4279-A577-2BF5506FFD66}" name="PivotTable4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Time" fld="3" subtotal="average" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48851351-5762-47AA-9C99-E48338352ED5}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Time" fld="3" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2856F446-3E7B-4854-B939-AF6EA7A2F56D}" name="Table2" displayName="Table2" ref="A1:I51" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2856F446-3E7B-4854-B939-AF6EA7A2F56D}" name="Table2" displayName="Table2" ref="A1:I51" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="A1:I51" xr:uid="{2856F446-3E7B-4854-B939-AF6EA7A2F56D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I51">
     <sortCondition ref="B1:B51"/>
@@ -388,7 +2487,7 @@
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{71450332-B3B5-4E96-86BB-34323B05ABC1}" name="Experiment Name"/>
     <tableColumn id="2" xr3:uid="{A51F0899-E2FA-42CE-92AF-944DD492BF74}" name="1D Shape"/>
-    <tableColumn id="3" xr3:uid="{66741120-6567-4F78-8D8C-82FB4A90D2FF}" name="Noise (%)" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{66741120-6567-4F78-8D8C-82FB4A90D2FF}" name="Noise (%)" dataDxfId="35"/>
     <tableColumn id="4" xr3:uid="{D7708E0C-FFAD-4A5D-9D36-E680B52AE3D6}" name="Solver Type"/>
     <tableColumn id="5" xr3:uid="{D0FAAAE8-66FD-4D21-986B-DE7577F2BC40}" name="Monotonicity"/>
     <tableColumn id="6" xr3:uid="{95EED547-3D6F-46C9-94E8-825FEFE177DF}" name="ω"/>
@@ -397,6 +2496,34 @@
     <tableColumn id="9" xr3:uid="{DF153323-ED2E-468D-A98C-278A6D0C7BA9}" name="Date"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{288A07A3-2F18-41C5-AE7D-0C571414E06A}" name="Table3" displayName="Table3" ref="A1:G61" totalsRowShown="0" headerRowDxfId="26" dataDxfId="27">
+  <autoFilter ref="A1:G61" xr:uid="{288A07A3-2F18-41C5-AE7D-0C571414E06A}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Composite Sine"/>
+        <filter val="Sin E"/>
+        <filter val="Sine"/>
+        <filter val="Step"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:G25">
+    <sortCondition ref="C1:C61"/>
+  </sortState>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4057DF9D-0784-4CA6-9760-7EB69DD81821}" name="Problem" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{09CDC94D-BD23-451A-968A-3536D32E02CF}" name="Data Type" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{01E7E663-6F07-43DA-8A9A-1C305518C38C}" name="Solver" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{A07A64D9-3E01-477C-8421-CFCC0CF38D50}" name="Time" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{87FB5476-73BB-44FC-8DA9-86505FDDD821}" name="RMSE " dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{6E00F914-CF6A-459C-8178-D1805481E3B7}" name="Max Error" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{7D03900D-C497-4240-A243-CA1190C77259}" name="Bound Error" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2036,4 +4163,2958 @@
     </mc:AlternateContent>
   </oleObjects>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E51C29-A20D-4E3A-99A1-490674FEE959}">
+  <dimension ref="A1:O72"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="18">
+        <v>70.881799999999998</v>
+      </c>
+      <c r="E2" s="19">
+        <v>8.0158078411725396E-5</v>
+      </c>
+      <c r="F2" s="19">
+        <v>3.0149357368290598E-4</v>
+      </c>
+      <c r="G2" s="19">
+        <v>5.63382571350472E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="24">
+        <v>16.0017</v>
+      </c>
+      <c r="E3" s="25">
+        <v>5.0852103951725701E-2</v>
+      </c>
+      <c r="F3" s="25">
+        <v>0.34232484116550099</v>
+      </c>
+      <c r="G3" s="25">
+        <v>0.67448009802876696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="21">
+        <v>61.017899999999997</v>
+      </c>
+      <c r="E4" s="22">
+        <v>1.0708893831739E-4</v>
+      </c>
+      <c r="F4" s="22">
+        <v>2.5131480007299601E-4</v>
+      </c>
+      <c r="G4" s="22">
+        <v>4.22915047950317E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="21">
+        <v>17.398199999999999</v>
+      </c>
+      <c r="E5" s="22">
+        <v>0.61338183564672499</v>
+      </c>
+      <c r="F5" s="22">
+        <v>2.9628652746893702</v>
+      </c>
+      <c r="G5" s="22">
+        <v>4.2693759980444002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="24">
+        <v>0.272123</v>
+      </c>
+      <c r="E6" s="25">
+        <v>5.5376499405338701E-4</v>
+      </c>
+      <c r="F6" s="25">
+        <v>1.5675444224314201E-3</v>
+      </c>
+      <c r="G6" s="25">
+        <v>2.7592100881690998E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="24">
+        <v>7.5115100000000004E-2</v>
+      </c>
+      <c r="E7" s="25">
+        <v>0.23048247046100401</v>
+      </c>
+      <c r="F7" s="25">
+        <v>1.5515994839971401</v>
+      </c>
+      <c r="G7" s="25">
+        <v>2.9870621343039798</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="21">
+        <v>13.916399999999999</v>
+      </c>
+      <c r="E8" s="22">
+        <v>7.4497472269780495E-5</v>
+      </c>
+      <c r="F8" s="22">
+        <v>3.65258340649205E-4</v>
+      </c>
+      <c r="G8" s="22">
+        <v>4.7883756930836501E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="21">
+        <v>5.0377299999999998</v>
+      </c>
+      <c r="E9" s="22">
+        <v>6.2147256965994498E-2</v>
+      </c>
+      <c r="F9" s="22">
+        <v>0.75542110204059698</v>
+      </c>
+      <c r="G9" s="22">
+        <v>1.3574724764266599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="24">
+        <v>12.635400000000001</v>
+      </c>
+      <c r="E10" s="25">
+        <v>1.82414863568795E-4</v>
+      </c>
+      <c r="F10" s="25">
+        <v>9.4711775251927197E-4</v>
+      </c>
+      <c r="G10" s="25">
+        <v>1.22394752256336E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="24">
+        <v>3.9053200000000001</v>
+      </c>
+      <c r="E11" s="25">
+        <v>6.6219476715996706E-2</v>
+      </c>
+      <c r="F11" s="25">
+        <v>0.41891422090307801</v>
+      </c>
+      <c r="G11" s="25">
+        <v>0.809559330529667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="21">
+        <v>1.9495819000000001</v>
+      </c>
+      <c r="E12" s="22">
+        <v>0.250117713343676</v>
+      </c>
+      <c r="F12" s="22">
+        <v>1.5741567529357801</v>
+      </c>
+      <c r="G12" s="22">
+        <v>2.8632267143095902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0.54042769999999996</v>
+      </c>
+      <c r="E13" s="22">
+        <v>0.217587732167494</v>
+      </c>
+      <c r="F13" s="22">
+        <v>1.40379689424623</v>
+      </c>
+      <c r="G13" s="22">
+        <v>2.72814040764188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="24">
+        <v>36.898899999999998</v>
+      </c>
+      <c r="E14" s="25">
+        <v>2.5091416902881399E-3</v>
+      </c>
+      <c r="F14" s="25">
+        <v>7.2222514734408497E-3</v>
+      </c>
+      <c r="G14" s="25">
+        <v>1.4113510787013899E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="24">
+        <v>7.8173300000000001</v>
+      </c>
+      <c r="E15" s="25">
+        <v>0.801291367502725</v>
+      </c>
+      <c r="F15" s="25">
+        <v>2.88919091353198</v>
+      </c>
+      <c r="G15" s="25">
+        <v>5.37246542255048</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="21">
+        <v>47.877200000000002</v>
+      </c>
+      <c r="E16" s="22">
+        <v>5.5010172994750901E-3</v>
+      </c>
+      <c r="F16" s="22">
+        <v>1.6524525225234801E-2</v>
+      </c>
+      <c r="G16" s="22">
+        <v>2.7843177139354601E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="21">
+        <v>7.7334100000000001</v>
+      </c>
+      <c r="E17" s="22">
+        <v>0.96598603616919898</v>
+      </c>
+      <c r="F17" s="22">
+        <v>3.5582416127633998</v>
+      </c>
+      <c r="G17" s="22">
+        <v>6.28696568810778</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="24">
+        <v>0.26216699999999998</v>
+      </c>
+      <c r="E18" s="25">
+        <v>6.6681803044133896E-3</v>
+      </c>
+      <c r="F18" s="25">
+        <v>2.0590593675692499E-2</v>
+      </c>
+      <c r="G18" s="25">
+        <v>2.3637880091791501E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="24">
+        <v>0.326992</v>
+      </c>
+      <c r="E19" s="25">
+        <v>2.4102050946459301</v>
+      </c>
+      <c r="F19" s="25">
+        <v>5.2920800991820203</v>
+      </c>
+      <c r="G19" s="25">
+        <v>6.77487680978372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="21">
+        <v>1.80654</v>
+      </c>
+      <c r="E20" s="22">
+        <v>2.6246408285867402E-3</v>
+      </c>
+      <c r="F20" s="22">
+        <v>7.3498517231258102E-3</v>
+      </c>
+      <c r="G20" s="22">
+        <v>1.4359291311023901E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="21">
+        <v>2.6439900000000001</v>
+      </c>
+      <c r="E21" s="22">
+        <v>0.77456738695982197</v>
+      </c>
+      <c r="F21" s="22">
+        <v>2.88986608068537</v>
+      </c>
+      <c r="G21" s="22">
+        <v>5.3199692641874696</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="24">
+        <v>2.7180300000000002</v>
+      </c>
+      <c r="E22" s="25">
+        <v>2.6246393560013302E-3</v>
+      </c>
+      <c r="F22" s="25">
+        <v>7.3498541312440697E-3</v>
+      </c>
+      <c r="G22" s="25">
+        <v>1.4359288182437299E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="24">
+        <v>0.98388299999999995</v>
+      </c>
+      <c r="E23" s="25">
+        <v>0.65760417888491196</v>
+      </c>
+      <c r="F23" s="25">
+        <v>2.4889104970683902</v>
+      </c>
+      <c r="G23" s="25">
+        <v>4.9520824509459498</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="21">
+        <v>4.3649449000000002</v>
+      </c>
+      <c r="E24" s="22">
+        <v>3.01868263179329E-3</v>
+      </c>
+      <c r="F24" s="22">
+        <v>9.0967723677438505E-3</v>
+      </c>
+      <c r="G24" s="22">
+        <v>1.7050883086645801E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="21">
+        <v>2.1352106000000002</v>
+      </c>
+      <c r="E25" s="22">
+        <v>1.3240908227252699</v>
+      </c>
+      <c r="F25" s="22">
+        <v>4.4642172980045904</v>
+      </c>
+      <c r="G25" s="22">
+        <v>7.7159285101947397</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="24">
+        <v>62.610999999999997</v>
+      </c>
+      <c r="E26" s="25">
+        <v>2.3646261766681201E-3</v>
+      </c>
+      <c r="F26" s="25">
+        <v>7.6746499836514602E-3</v>
+      </c>
+      <c r="G26" s="25">
+        <v>1.2810808666554801E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="21">
+        <v>54.771299999999997</v>
+      </c>
+      <c r="E27" s="22">
+        <v>1.1550009147432601E-3</v>
+      </c>
+      <c r="F27" s="22">
+        <v>3.2988905937129001E-3</v>
+      </c>
+      <c r="G27" s="22">
+        <v>6.5095841618804896E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="24">
+        <v>0.34911399999999998</v>
+      </c>
+      <c r="E28" s="25">
+        <v>6.9063927253939996E-4</v>
+      </c>
+      <c r="F28" s="25">
+        <v>2.3405484709488802E-3</v>
+      </c>
+      <c r="G28" s="25">
+        <v>3.9843163903979101E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="21">
+        <v>2.87683</v>
+      </c>
+      <c r="E29" s="22">
+        <v>2.1818662183589101E-3</v>
+      </c>
+      <c r="F29" s="22">
+        <v>7.8308685916167308E-3</v>
+      </c>
+      <c r="G29" s="22">
+        <v>1.2375491780561699E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="24">
+        <v>4.4576900000000004</v>
+      </c>
+      <c r="E30" s="25">
+        <v>1.9557646257379298E-3</v>
+      </c>
+      <c r="F30" s="25">
+        <v>6.7816752973434303E-3</v>
+      </c>
+      <c r="G30" s="25">
+        <v>1.12395882886645E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="21">
+        <v>4.0496929000000002</v>
+      </c>
+      <c r="E31" s="22">
+        <v>1.93825715071022E-3</v>
+      </c>
+      <c r="F31" s="22">
+        <v>6.4403342578306603E-3</v>
+      </c>
+      <c r="G31" s="22">
+        <v>1.1390192968623499E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="24">
+        <v>8.5870700000000006</v>
+      </c>
+      <c r="E32" s="25">
+        <v>4.1453415836221599E-2</v>
+      </c>
+      <c r="F32" s="25">
+        <v>0.14040456794717501</v>
+      </c>
+      <c r="G32" s="25">
+        <v>0.245064119550231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="21">
+        <v>14.228300000000001</v>
+      </c>
+      <c r="E33" s="22">
+        <v>0.13904915029484899</v>
+      </c>
+      <c r="F33" s="22">
+        <v>0.386911454156115</v>
+      </c>
+      <c r="G33" s="22">
+        <v>0.68318059147913801</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="24">
+        <v>7.0940500000000004E-2</v>
+      </c>
+      <c r="E34" s="25">
+        <v>0.15612056582273201</v>
+      </c>
+      <c r="F34" s="25">
+        <v>0.51286766610365897</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0.71278513265916699</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="21">
+        <v>1.6848399999999999</v>
+      </c>
+      <c r="E35" s="22">
+        <v>4.1456865722321698E-2</v>
+      </c>
+      <c r="F35" s="22">
+        <v>0.140393759291254</v>
+      </c>
+      <c r="G35" s="22">
+        <v>0.24506370248391099</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="24">
+        <v>1.5675600000000001</v>
+      </c>
+      <c r="E36" s="25">
+        <v>4.0833320272044303E-2</v>
+      </c>
+      <c r="F36" s="25">
+        <v>0.140925650846046</v>
+      </c>
+      <c r="G36" s="25">
+        <v>0.24505734285731401</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="21">
+        <v>1.2574320000000001</v>
+      </c>
+      <c r="E37" s="22">
+        <v>4.0787048159407598E-2</v>
+      </c>
+      <c r="F37" s="22">
+        <v>0.14148670760075799</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.245053054690517</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="24">
+        <v>54.652799999999999</v>
+      </c>
+      <c r="E38" s="25">
+        <v>4.4510542736962699E-3</v>
+      </c>
+      <c r="F38" s="25">
+        <v>1.6507426046054201E-2</v>
+      </c>
+      <c r="G38" s="25">
+        <v>2.6229440676767898E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="21">
+        <v>63.719700000000003</v>
+      </c>
+      <c r="E39" s="22">
+        <v>6.3331295728659403E-3</v>
+      </c>
+      <c r="F39" s="22">
+        <v>1.7931398656809299E-2</v>
+      </c>
+      <c r="G39" s="22">
+        <v>3.3279032323531001E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="24">
+        <v>0.33784500000000001</v>
+      </c>
+      <c r="E40" s="25">
+        <v>1.8309538424324302E-2</v>
+      </c>
+      <c r="F40" s="25">
+        <v>8.5810910075569402E-2</v>
+      </c>
+      <c r="G40" s="25">
+        <v>8.5895394944806996E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="21">
+        <v>2.5577700000000001</v>
+      </c>
+      <c r="E41" s="22">
+        <v>4.0142921929919003E-3</v>
+      </c>
+      <c r="F41" s="22">
+        <v>1.28594873147887E-2</v>
+      </c>
+      <c r="G41" s="22">
+        <v>2.28128592064397E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="24">
+        <v>3.11145</v>
+      </c>
+      <c r="E42" s="25">
+        <v>4.0142916824074297E-3</v>
+      </c>
+      <c r="F42" s="25">
+        <v>1.28594959878779E-2</v>
+      </c>
+      <c r="G42" s="25">
+        <v>2.28128717828079E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="21">
+        <v>4.5974335000000002</v>
+      </c>
+      <c r="E43" s="22">
+        <v>5.5891524503640499E-3</v>
+      </c>
+      <c r="F43" s="22">
+        <v>2.2443603715458799E-2</v>
+      </c>
+      <c r="G43" s="22">
+        <v>3.4773400574761498E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="24">
+        <v>6.6707299999999998</v>
+      </c>
+      <c r="E44" s="25">
+        <v>0.24360513166502101</v>
+      </c>
+      <c r="F44" s="25">
+        <v>0.75915050824021502</v>
+      </c>
+      <c r="G44" s="25">
+        <v>1.51023010747413</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="21">
+        <v>13.828099999999999</v>
+      </c>
+      <c r="E45" s="22">
+        <v>0.45993125581394501</v>
+      </c>
+      <c r="F45" s="22">
+        <v>1.88492546748256</v>
+      </c>
+      <c r="G45" s="22">
+        <v>3.0087160259682402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="24">
+        <v>8.8483400000000004E-2</v>
+      </c>
+      <c r="E46" s="25">
+        <v>0.50439958268898499</v>
+      </c>
+      <c r="F46" s="25">
+        <v>1.17428808388124</v>
+      </c>
+      <c r="G46" s="25">
+        <v>1.8642873922166101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="21">
+        <v>1.0792299999999999</v>
+      </c>
+      <c r="E47" s="22">
+        <v>0.23694535093489999</v>
+      </c>
+      <c r="F47" s="22">
+        <v>0.75638934371671995</v>
+      </c>
+      <c r="G47" s="22">
+        <v>1.51030932819276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="24">
+        <v>1.5731599999999999</v>
+      </c>
+      <c r="E48" s="25">
+        <v>0.229718036094717</v>
+      </c>
+      <c r="F48" s="25">
+        <v>0.77961498364586002</v>
+      </c>
+      <c r="G48" s="25">
+        <v>1.4616668194278799</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A49" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="21">
+        <v>1.5713614</v>
+      </c>
+      <c r="E49" s="22">
+        <v>0.40071241252664902</v>
+      </c>
+      <c r="F49" s="22">
+        <v>0.96581405788355201</v>
+      </c>
+      <c r="G49" s="22">
+        <v>1.9214747959175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A50" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="24">
+        <v>6.6156800000000002</v>
+      </c>
+      <c r="E50" s="25">
+        <v>0.14592883124204001</v>
+      </c>
+      <c r="F50" s="25">
+        <v>0.60449260703643604</v>
+      </c>
+      <c r="G50" s="25">
+        <v>1.0055006730877001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A51" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="21">
+        <v>35.988700000000001</v>
+      </c>
+      <c r="E51" s="22">
+        <v>0.12968113651434601</v>
+      </c>
+      <c r="F51" s="22">
+        <v>0.57749149831848201</v>
+      </c>
+      <c r="G51" s="22">
+        <v>1.0185314034547699</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A52" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="24">
+        <v>0.292354</v>
+      </c>
+      <c r="E52" s="25">
+        <v>0.31220361801305802</v>
+      </c>
+      <c r="F52" s="25">
+        <v>0.73540788758055997</v>
+      </c>
+      <c r="G52" s="25">
+        <v>0.73616458940486895</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A53" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="21">
+        <v>13.1905</v>
+      </c>
+      <c r="E53" s="22">
+        <v>3.3790369124594198E-3</v>
+      </c>
+      <c r="F53" s="22">
+        <v>1.0685154303572E-2</v>
+      </c>
+      <c r="G53" s="22">
+        <v>1.9292474326642099E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A54" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D54" s="24">
+        <v>1.1140000000000001</v>
+      </c>
+      <c r="E54" s="25">
+        <v>0.249127964789603</v>
+      </c>
+      <c r="F54" s="25">
+        <v>0.88938504322949796</v>
+      </c>
+      <c r="G54" s="25">
+        <v>1.3298393318872299</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A55" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="21">
+        <v>1.9451883000000001</v>
+      </c>
+      <c r="E55" s="22">
+        <v>0.40359911336578402</v>
+      </c>
+      <c r="F55" s="22">
+        <v>0.62498700848665001</v>
+      </c>
+      <c r="G55" s="22">
+        <v>1.1677899083337999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A56" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="24">
+        <v>9.6140600000000003</v>
+      </c>
+      <c r="E56" s="25">
+        <v>9.8471561707902805E-2</v>
+      </c>
+      <c r="F56" s="25">
+        <v>0.33753961371707603</v>
+      </c>
+      <c r="G56" s="25">
+        <v>0.61523698654407699</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A57" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="21">
+        <v>17.239699999999999</v>
+      </c>
+      <c r="E57" s="22">
+        <v>0.14224438082638899</v>
+      </c>
+      <c r="F57" s="22">
+        <v>0.414745195132116</v>
+      </c>
+      <c r="G57" s="22">
+        <v>0.80134390579414105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A58" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="24">
+        <v>6.8042199999999997E-2</v>
+      </c>
+      <c r="E58" s="25">
+        <v>0.50760907712574199</v>
+      </c>
+      <c r="F58" s="25">
+        <v>1.09124651945925</v>
+      </c>
+      <c r="G58" s="25">
+        <v>1.10549516064681</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A59" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="21">
+        <v>3.1019899999999998</v>
+      </c>
+      <c r="E59" s="22">
+        <v>9.8036203584847603E-2</v>
+      </c>
+      <c r="F59" s="22">
+        <v>0.30778567176863803</v>
+      </c>
+      <c r="G59" s="22">
+        <v>0.58570046607555803</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D60" s="24">
+        <v>2.7850799999999998</v>
+      </c>
+      <c r="E60" s="25">
+        <v>9.71806155299062E-2</v>
+      </c>
+      <c r="F60" s="25">
+        <v>0.295448031130705</v>
+      </c>
+      <c r="G60" s="25">
+        <v>0.57115690156416798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D61" s="21">
+        <v>0.69017720000000005</v>
+      </c>
+      <c r="E61" s="22">
+        <v>0.131432654739953</v>
+      </c>
+      <c r="F61" s="22">
+        <v>0.54299357139798299</v>
+      </c>
+      <c r="G61" s="22">
+        <v>1.0098621954920799</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K62" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K65" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L65" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" t="s">
+        <v>65</v>
+      </c>
+      <c r="N65" t="s">
+        <v>66</v>
+      </c>
+      <c r="O65" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K66" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L66" s="11">
+        <v>28.035107</v>
+      </c>
+      <c r="M66" s="12">
+        <v>0.13910073921247004</v>
+      </c>
+      <c r="N66" s="12">
+        <v>0.51048088727152119</v>
+      </c>
+      <c r="O66" s="12">
+        <v>0.94766945499370725</v>
+      </c>
+    </row>
+    <row r="67" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K67" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67" s="11">
+        <v>33.380251000000001</v>
+      </c>
+      <c r="M67" s="12">
+        <v>0.24633700319908547</v>
+      </c>
+      <c r="N67" s="12">
+        <v>0.98231866318178729</v>
+      </c>
+      <c r="O67" s="12">
+        <v>1.6136168321521187</v>
+      </c>
+    </row>
+    <row r="68" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K68" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="11">
+        <v>0.21431762000000001</v>
+      </c>
+      <c r="M68" s="12">
+        <v>0.41472425317527806</v>
+      </c>
+      <c r="N68" s="12">
+        <v>1.0467799336848513</v>
+      </c>
+      <c r="O68" s="12">
+        <v>1.429694802053032</v>
+      </c>
+    </row>
+    <row r="69" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K69" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="L69" s="11">
+        <v>4.7895820000000002</v>
+      </c>
+      <c r="M69" s="12">
+        <v>0.12254273977925523</v>
+      </c>
+      <c r="N69" s="12">
+        <v>0.48889465777763313</v>
+      </c>
+      <c r="O69" s="12">
+        <v>0.90878341915603333</v>
+      </c>
+    </row>
+    <row r="70" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K70" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L70" s="11">
+        <v>3.4851573</v>
+      </c>
+      <c r="M70" s="12">
+        <v>0.13494607028148947</v>
+      </c>
+      <c r="N70" s="12">
+        <v>0.50411365699925614</v>
+      </c>
+      <c r="O70" s="12">
+        <v>0.94189978729886814</v>
+      </c>
+    </row>
+    <row r="71" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K71" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L71" s="11">
+        <v>2.3101450400000005</v>
+      </c>
+      <c r="M71" s="12">
+        <v>0.27788735892611011</v>
+      </c>
+      <c r="N71" s="12">
+        <v>0.97554330008965773</v>
+      </c>
+      <c r="O71" s="12">
+        <v>1.7714690063210139</v>
+      </c>
+    </row>
+    <row r="72" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="K72" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L72" s="11">
+        <v>12.035759993333333</v>
+      </c>
+      <c r="M72" s="10">
+        <v>0.22258969409561474</v>
+      </c>
+      <c r="N72" s="10">
+        <v>0.75135518316745076</v>
+      </c>
+      <c r="O72" s="10">
+        <v>1.268855550329129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FED1F608-920C-4CE7-BD84-4D506B6A3AD2}">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="9">
+        <v>29.022560999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="9">
+        <v>32.52543099999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.21369023000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="9">
+        <v>4.8820490000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="9">
+        <v>3.6192212999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="9">
+        <v>14.052590505999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12347F2-F5CA-471E-AECC-8A1733301BEF}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="9">
+        <v>20.114168810000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="9">
+        <v>10.906844200000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="9">
+        <v>15.12046445</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="9">
+        <v>15.12046445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="9">
+        <v>9.0010106199999989</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="9">
+        <v>14.052590506000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86632860-7E0F-4643-B153-B9007F331D73}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="21.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2">
+        <v>6.6681803044133896E-3</v>
+      </c>
+      <c r="E2">
+        <v>2.0590593675692499E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.3637880091791501E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>2.6246393560013302E-3</v>
+      </c>
+      <c r="E3">
+        <v>7.3498541312440697E-3</v>
+      </c>
+      <c r="F3">
+        <v>1.4359288182437299E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4">
+        <v>3.01868263179329E-3</v>
+      </c>
+      <c r="E4">
+        <v>9.0967723677438505E-3</v>
+      </c>
+      <c r="F4">
+        <v>1.7050883086645801E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5">
+        <v>2.6246408285867402E-3</v>
+      </c>
+      <c r="E5">
+        <v>7.3498517231258102E-3</v>
+      </c>
+      <c r="F5">
+        <v>1.4359291311023901E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6">
+        <v>2.5091416902881399E-3</v>
+      </c>
+      <c r="E6">
+        <v>7.2222514734408497E-3</v>
+      </c>
+      <c r="F6">
+        <v>1.4113510787013899E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7">
+        <v>5.5010172994750901E-3</v>
+      </c>
+      <c r="E7">
+        <v>1.6524525225234801E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.7843177139354601E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8">
+        <v>2.4102050946459301</v>
+      </c>
+      <c r="E8">
+        <v>5.2920800991820203</v>
+      </c>
+      <c r="F8">
+        <v>6.77487680978372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9">
+        <v>0.65760417888491196</v>
+      </c>
+      <c r="E9">
+        <v>2.4889104970683902</v>
+      </c>
+      <c r="F9">
+        <v>4.9520824509459498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10">
+        <v>1.3240908227252699</v>
+      </c>
+      <c r="E10">
+        <v>4.4642172980045904</v>
+      </c>
+      <c r="F10">
+        <v>7.7159285101947397</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11">
+        <v>0.77456738695982197</v>
+      </c>
+      <c r="E11">
+        <v>2.88986608068537</v>
+      </c>
+      <c r="F11">
+        <v>5.3199692641874696</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12">
+        <v>0.801291367502725</v>
+      </c>
+      <c r="E12">
+        <v>2.88919091353198</v>
+      </c>
+      <c r="F12">
+        <v>5.37246542255048</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13">
+        <v>0.96598603616919898</v>
+      </c>
+      <c r="E13">
+        <v>3.5582416127633998</v>
+      </c>
+      <c r="F13">
+        <v>6.28696568810778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14">
+        <v>1.8309538424324302E-2</v>
+      </c>
+      <c r="E14">
+        <v>8.5810910075569402E-2</v>
+      </c>
+      <c r="F14">
+        <v>8.5895394944806996E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15">
+        <v>4.0142916824074297E-3</v>
+      </c>
+      <c r="E15">
+        <v>1.28594959878779E-2</v>
+      </c>
+      <c r="F15">
+        <v>2.28128717828079E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16">
+        <v>5.5891524503640499E-3</v>
+      </c>
+      <c r="E16">
+        <v>2.2443603715458799E-2</v>
+      </c>
+      <c r="F16">
+        <v>3.4773400574761498E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17">
+        <v>4.0142921929919003E-3</v>
+      </c>
+      <c r="E17">
+        <v>1.28594873147887E-2</v>
+      </c>
+      <c r="F17">
+        <v>2.28128592064397E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18">
+        <v>4.4510542736962699E-3</v>
+      </c>
+      <c r="E18">
+        <v>1.6507426046054201E-2</v>
+      </c>
+      <c r="F18">
+        <v>2.6229440676767898E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19">
+        <v>6.3331295728659403E-3</v>
+      </c>
+      <c r="E19">
+        <v>1.7931398656809299E-2</v>
+      </c>
+      <c r="F19">
+        <v>3.3279032323531001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20">
+        <v>0.50439958268898499</v>
+      </c>
+      <c r="E20">
+        <v>1.17428808388124</v>
+      </c>
+      <c r="F20">
+        <v>1.8642873922166101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21">
+        <v>0.229718036094717</v>
+      </c>
+      <c r="E21">
+        <v>0.77961498364586002</v>
+      </c>
+      <c r="F21">
+        <v>1.4616668194278799</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22">
+        <v>0.40071241252664902</v>
+      </c>
+      <c r="E22">
+        <v>0.96581405788355201</v>
+      </c>
+      <c r="F22">
+        <v>1.9214747959175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23">
+        <v>0.23694535093489999</v>
+      </c>
+      <c r="E23">
+        <v>0.75638934371671995</v>
+      </c>
+      <c r="F23">
+        <v>1.51030932819276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24">
+        <v>0.24360513166502101</v>
+      </c>
+      <c r="E24">
+        <v>0.75915050824021502</v>
+      </c>
+      <c r="F24">
+        <v>1.51023010747413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25">
+        <v>0.45993125581394501</v>
+      </c>
+      <c r="E25">
+        <v>1.88492546748256</v>
+      </c>
+      <c r="F25">
+        <v>3.0087160259682402</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26">
+        <v>0.31220361801305802</v>
+      </c>
+      <c r="E26">
+        <v>0.73540788758055997</v>
+      </c>
+      <c r="F26">
+        <v>0.73616458940486895</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27">
+        <v>0.249127964789603</v>
+      </c>
+      <c r="E27">
+        <v>0.88938504322949796</v>
+      </c>
+      <c r="F27">
+        <v>1.3298393318872299</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28">
+        <v>0.40359911336578402</v>
+      </c>
+      <c r="E28">
+        <v>0.62498700848665001</v>
+      </c>
+      <c r="F28">
+        <v>1.1677899083337999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29">
+        <v>3.3790369124594198E-3</v>
+      </c>
+      <c r="E29">
+        <v>1.0685154303572E-2</v>
+      </c>
+      <c r="F29">
+        <v>1.9292474326642099E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30">
+        <v>0.14592883124204001</v>
+      </c>
+      <c r="E30">
+        <v>0.60449260703643604</v>
+      </c>
+      <c r="F30">
+        <v>1.0055006730877001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>0.12968113651434601</v>
+      </c>
+      <c r="E31">
+        <v>0.57749149831848201</v>
+      </c>
+      <c r="F31">
+        <v>1.0185314034547699</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32">
+        <v>0.50760907712574199</v>
+      </c>
+      <c r="E32">
+        <v>1.09124651945925</v>
+      </c>
+      <c r="F32">
+        <v>1.10549516064681</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33">
+        <v>9.71806155299062E-2</v>
+      </c>
+      <c r="E33">
+        <v>0.295448031130705</v>
+      </c>
+      <c r="F33">
+        <v>0.57115690156416798</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34">
+        <v>0.131432654739953</v>
+      </c>
+      <c r="E34">
+        <v>0.54299357139798299</v>
+      </c>
+      <c r="F34">
+        <v>1.0098621954920799</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35">
+        <v>9.8036203584847603E-2</v>
+      </c>
+      <c r="E35">
+        <v>0.30778567176863803</v>
+      </c>
+      <c r="F35">
+        <v>0.58570046607555803</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36">
+        <v>9.8471561707902805E-2</v>
+      </c>
+      <c r="E36">
+        <v>0.33753961371707603</v>
+      </c>
+      <c r="F36">
+        <v>0.61523698654407699</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37">
+        <v>0.14224438082638899</v>
+      </c>
+      <c r="E37">
+        <v>0.414745195132116</v>
+      </c>
+      <c r="F37">
+        <v>0.80134390579414105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>6.9063927253939996E-4</v>
+      </c>
+      <c r="E38">
+        <v>2.3405484709488802E-3</v>
+      </c>
+      <c r="F38">
+        <v>3.9843163903979101E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39">
+        <v>1.9557646257379298E-3</v>
+      </c>
+      <c r="E39">
+        <v>6.7816752973434303E-3</v>
+      </c>
+      <c r="F39">
+        <v>1.12395882886645E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40">
+        <v>1.93825715071022E-3</v>
+      </c>
+      <c r="E40">
+        <v>6.4403342578306603E-3</v>
+      </c>
+      <c r="F40">
+        <v>1.1390192968623499E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41">
+        <v>2.1818662183589101E-3</v>
+      </c>
+      <c r="E41">
+        <v>7.8308685916167308E-3</v>
+      </c>
+      <c r="F41">
+        <v>1.2375491780561699E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42">
+        <v>2.3646261766681201E-3</v>
+      </c>
+      <c r="E42">
+        <v>7.6746499836514602E-3</v>
+      </c>
+      <c r="F42">
+        <v>1.2810808666554801E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43">
+        <v>1.1550009147432601E-3</v>
+      </c>
+      <c r="E43">
+        <v>3.2988905937129001E-3</v>
+      </c>
+      <c r="F43">
+        <v>6.5095841618804896E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44">
+        <v>0.15612056582273201</v>
+      </c>
+      <c r="E44">
+        <v>0.51286766610365897</v>
+      </c>
+      <c r="F44">
+        <v>0.71278513265916699</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45">
+        <v>4.0833320272044303E-2</v>
+      </c>
+      <c r="E45">
+        <v>0.140925650846046</v>
+      </c>
+      <c r="F45">
+        <v>0.24505734285731401</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46">
+        <v>4.0787048159407598E-2</v>
+      </c>
+      <c r="E46">
+        <v>0.14148670760075799</v>
+      </c>
+      <c r="F46">
+        <v>0.245053054690517</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47">
+        <v>4.1456865722321698E-2</v>
+      </c>
+      <c r="E47">
+        <v>0.140393759291254</v>
+      </c>
+      <c r="F47">
+        <v>0.24506370248391099</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48">
+        <v>4.1453415836221599E-2</v>
+      </c>
+      <c r="E48">
+        <v>0.14040456794717501</v>
+      </c>
+      <c r="F48">
+        <v>0.245064119550231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49">
+        <v>0.13904915029484899</v>
+      </c>
+      <c r="E49">
+        <v>0.386911454156115</v>
+      </c>
+      <c r="F49">
+        <v>0.68318059147913801</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50">
+        <v>5.5376499405338701E-4</v>
+      </c>
+      <c r="E50">
+        <v>1.5675444224314201E-3</v>
+      </c>
+      <c r="F50">
+        <v>2.7592100881690998E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51">
+        <v>1.82414863568795E-4</v>
+      </c>
+      <c r="E51">
+        <v>9.4711775251927197E-4</v>
+      </c>
+      <c r="F51">
+        <v>1.22394752256336E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52">
+        <v>0.250117713343676</v>
+      </c>
+      <c r="E52">
+        <v>1.5741567529357801</v>
+      </c>
+      <c r="F52">
+        <v>2.8632267143095902</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" t="s">
+        <v>64</v>
+      </c>
+      <c r="D53" s="10">
+        <v>7.4497472269780495E-5</v>
+      </c>
+      <c r="E53">
+        <v>3.65258340649205E-4</v>
+      </c>
+      <c r="F53">
+        <v>4.7883756930836501E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D54" s="10">
+        <v>8.0158078411725396E-5</v>
+      </c>
+      <c r="E54">
+        <v>3.0149357368290598E-4</v>
+      </c>
+      <c r="F54">
+        <v>5.63382571350472E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55">
+        <v>1.0708893831739E-4</v>
+      </c>
+      <c r="E55">
+        <v>2.5131480007299601E-4</v>
+      </c>
+      <c r="F55">
+        <v>4.22915047950317E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56">
+        <v>0.23048247046100401</v>
+      </c>
+      <c r="E56">
+        <v>1.5515994839971401</v>
+      </c>
+      <c r="F56">
+        <v>2.9870621343039798</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57">
+        <v>6.6219476715996706E-2</v>
+      </c>
+      <c r="E57">
+        <v>0.41891422090307801</v>
+      </c>
+      <c r="F57">
+        <v>0.809559330529667</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58">
+        <v>0.217587732167494</v>
+      </c>
+      <c r="E58">
+        <v>1.40379689424623</v>
+      </c>
+      <c r="F58">
+        <v>2.72814040764188</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59">
+        <v>6.2147256965994498E-2</v>
+      </c>
+      <c r="E59">
+        <v>0.75542110204059698</v>
+      </c>
+      <c r="F59">
+        <v>1.3574724764266599</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D60">
+        <v>5.0852103951725701E-2</v>
+      </c>
+      <c r="E60">
+        <v>0.34232484116550099</v>
+      </c>
+      <c r="F60">
+        <v>0.67448009802876696</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+      <c r="D61">
+        <v>0.61338183564672499</v>
+      </c>
+      <c r="E61">
+        <v>2.9628652746893702</v>
+      </c>
+      <c r="F61">
+        <v>4.2693759980444002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Results/ThesisExperimentList.xlsx
+++ b/Results/ThesisExperimentList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\MS_BSU\SLFA_Julia\ThesisExperiments\BradenKingThesis\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A25383-BAB9-4C08-BC5E-C31844334BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54718FE-3BA9-41B4-863B-BCE3ABB29C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" firstSheet="1" activeTab="2" xr2:uid="{C4202BFB-F5A2-4916-9270-58B282AAFCCC}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="71">
   <si>
     <t>1D Shape</t>
   </si>
@@ -257,6 +257,12 @@
   <si>
     <t>(All)</t>
   </si>
+  <si>
+    <t>ekek</t>
+  </si>
+  <si>
+    <t>oo</t>
+  </si>
 </sst>
 </file>
 
@@ -326,11 +332,63 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -387,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -400,7 +458,11 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -409,19 +471,20 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2504,10 +2567,12 @@
   <autoFilter ref="A1:G61" xr:uid="{288A07A3-2F18-41C5-AE7D-0C571414E06A}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Composite Sine"/>
-        <filter val="Sin E"/>
-        <filter val="Sine"/>
-        <filter val="Step"/>
+        <filter val="AsymmetricRBF"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="noisy"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4167,7 +4232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3E51C29-A20D-4E3A-99A1-490674FEE959}">
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -4183,1410 +4248,1410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" hidden="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="23">
         <v>70.881799999999998</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="24">
         <v>8.0158078411725396E-5</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="24">
         <v>3.0149357368290598E-4</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="24">
         <v>5.63382571350472E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="29">
         <v>16.0017</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="30">
         <v>5.0852103951725701E-2</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="30">
         <v>0.34232484116550099</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="30">
         <v>0.67448009802876696</v>
       </c>
     </row>
     <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="26">
         <v>61.017899999999997</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="27">
         <v>1.0708893831739E-4</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="27">
         <v>2.5131480007299601E-4</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="27">
         <v>4.22915047950317E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="26">
         <v>17.398199999999999</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="27">
         <v>0.61338183564672499</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="27">
         <v>2.9628652746893702</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="27">
         <v>4.2693759980444002</v>
       </c>
     </row>
     <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="29">
         <v>0.272123</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="30">
         <v>5.5376499405338701E-4</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="30">
         <v>1.5675444224314201E-3</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="30">
         <v>2.7592100881690998E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="29">
         <v>7.5115100000000004E-2</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="30">
         <v>0.23048247046100401</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="30">
         <v>1.5515994839971401</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="30">
         <v>2.9870621343039798</v>
       </c>
     </row>
     <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="26">
         <v>13.916399999999999</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="27">
         <v>7.4497472269780495E-5</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="27">
         <v>3.65258340649205E-4</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="27">
         <v>4.7883756930836501E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="26">
         <v>5.0377299999999998</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="27">
         <v>6.2147256965994498E-2</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="27">
         <v>0.75542110204059698</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="27">
         <v>1.3574724764266599</v>
       </c>
     </row>
     <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="29">
         <v>12.635400000000001</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="30">
         <v>1.82414863568795E-4</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="30">
         <v>9.4711775251927197E-4</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="30">
         <v>1.22394752256336E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="29">
         <v>3.9053200000000001</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="30">
         <v>6.6219476715996706E-2</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="30">
         <v>0.41891422090307801</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="30">
         <v>0.809559330529667</v>
       </c>
     </row>
     <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="26">
         <v>1.9495819000000001</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="27">
         <v>0.250117713343676</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="27">
         <v>1.5741567529357801</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="27">
         <v>2.8632267143095902</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="26">
         <v>0.54042769999999996</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="27">
         <v>0.217587732167494</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="27">
         <v>1.40379689424623</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="27">
         <v>2.72814040764188</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="29">
         <v>36.898899999999998</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="30">
         <v>2.5091416902881399E-3</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="30">
         <v>7.2222514734408497E-3</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="30">
         <v>1.4113510787013899E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="29">
         <v>7.8173300000000001</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="30">
         <v>0.801291367502725</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="30">
         <v>2.88919091353198</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="30">
         <v>5.37246542255048</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="26">
         <v>47.877200000000002</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="27">
         <v>5.5010172994750901E-3</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="27">
         <v>1.6524525225234801E-2</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="27">
         <v>2.7843177139354601E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="26">
         <v>7.7334100000000001</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="27">
         <v>0.96598603616919898</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="27">
         <v>3.5582416127633998</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="27">
         <v>6.28696568810778</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="29">
         <v>0.26216699999999998</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="30">
         <v>6.6681803044133896E-3</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="30">
         <v>2.0590593675692499E-2</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="30">
         <v>2.3637880091791501E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="29">
         <v>0.326992</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="30">
         <v>2.4102050946459301</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="30">
         <v>5.2920800991820203</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="30">
         <v>6.77487680978372</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="26">
         <v>1.80654</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="27">
         <v>2.6246408285867402E-3</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="27">
         <v>7.3498517231258102E-3</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="27">
         <v>1.4359291311023901E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="26">
         <v>2.6439900000000001</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="27">
         <v>0.77456738695982197</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="27">
         <v>2.88986608068537</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="27">
         <v>5.3199692641874696</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="23" t="s">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="29">
         <v>2.7180300000000002</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="30">
         <v>2.6246393560013302E-3</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="30">
         <v>7.3498541312440697E-3</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="30">
         <v>1.4359288182437299E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="23" t="s">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="29">
         <v>0.98388299999999995</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="30">
         <v>0.65760417888491196</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="30">
         <v>2.4889104970683902</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="30">
         <v>4.9520824509459498</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="26">
         <v>4.3649449000000002</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="27">
         <v>3.01868263179329E-3</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="27">
         <v>9.0967723677438505E-3</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="27">
         <v>1.7050883086645801E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="20" t="s">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="26">
         <v>2.1352106000000002</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="27">
         <v>1.3240908227252699</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="27">
         <v>4.4642172980045904</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="27">
         <v>7.7159285101947397</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="23" t="s">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="29">
         <v>62.610999999999997</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="30">
         <v>2.3646261766681201E-3</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="30">
         <v>7.6746499836514602E-3</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="30">
         <v>1.2810808666554801E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="20" t="s">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="26">
         <v>54.771299999999997</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="27">
         <v>1.1550009147432601E-3</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="27">
         <v>3.2988905937129001E-3</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="27">
         <v>6.5095841618804896E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" s="23" t="s">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="29">
         <v>0.34911399999999998</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="30">
         <v>6.9063927253939996E-4</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="30">
         <v>2.3405484709488802E-3</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="30">
         <v>3.9843163903979101E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D29" s="26">
         <v>2.87683</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="27">
         <v>2.1818662183589101E-3</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="27">
         <v>7.8308685916167308E-3</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="27">
         <v>1.2375491780561699E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="23" t="s">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="29">
         <v>4.4576900000000004</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="30">
         <v>1.9557646257379298E-3</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="30">
         <v>6.7816752973434303E-3</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="30">
         <v>1.12395882886645E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="20" t="s">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="21">
+      <c r="D31" s="26">
         <v>4.0496929000000002</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="27">
         <v>1.93825715071022E-3</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="27">
         <v>6.4403342578306603E-3</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="27">
         <v>1.1390192968623499E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="29">
         <v>8.5870700000000006</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="30">
         <v>4.1453415836221599E-2</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="30">
         <v>0.14040456794717501</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="30">
         <v>0.245064119550231</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="21">
+      <c r="D33" s="26">
         <v>14.228300000000001</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="27">
         <v>0.13904915029484899</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="27">
         <v>0.386911454156115</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="27">
         <v>0.68318059147913801</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" s="23" t="s">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="29">
         <v>7.0940500000000004E-2</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="30">
         <v>0.15612056582273201</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="30">
         <v>0.51286766610365897</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="30">
         <v>0.71278513265916699</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" s="20" t="s">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="21">
+      <c r="D35" s="26">
         <v>1.6848399999999999</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="27">
         <v>4.1456865722321698E-2</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="27">
         <v>0.140393759291254</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="27">
         <v>0.24506370248391099</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="23" t="s">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="29">
         <v>1.5675600000000001</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="30">
         <v>4.0833320272044303E-2</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="30">
         <v>0.140925650846046</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="30">
         <v>0.24505734285731401</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="20" t="s">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="21">
+      <c r="D37" s="26">
         <v>1.2574320000000001</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="27">
         <v>4.0787048159407598E-2</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="27">
         <v>0.14148670760075799</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="27">
         <v>0.245053054690517</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="23" t="s">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="29">
         <v>54.652799999999999</v>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="30">
         <v>4.4510542736962699E-3</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="30">
         <v>1.6507426046054201E-2</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="30">
         <v>2.6229440676767898E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="21">
+      <c r="D39" s="26">
         <v>63.719700000000003</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="27">
         <v>6.3331295728659403E-3</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="27">
         <v>1.7931398656809299E-2</v>
       </c>
-      <c r="G39" s="22">
+      <c r="G39" s="27">
         <v>3.3279032323531001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="23" t="s">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="29">
         <v>0.33784500000000001</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="30">
         <v>1.8309538424324302E-2</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="30">
         <v>8.5810910075569402E-2</v>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="30">
         <v>8.5895394944806996E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="20" t="s">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="26">
         <v>2.5577700000000001</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="27">
         <v>4.0142921929919003E-3</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="27">
         <v>1.28594873147887E-2</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="27">
         <v>2.28128592064397E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" s="23" t="s">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D42" s="24">
+      <c r="D42" s="29">
         <v>3.11145</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="30">
         <v>4.0142916824074297E-3</v>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="30">
         <v>1.28594959878779E-2</v>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="30">
         <v>2.28128717828079E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" s="20" t="s">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="26">
         <v>4.5974335000000002</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="27">
         <v>5.5891524503640499E-3</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="27">
         <v>2.2443603715458799E-2</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="27">
         <v>3.4773400574761498E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="23" t="s">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="24">
+      <c r="D44" s="29">
         <v>6.6707299999999998</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="30">
         <v>0.24360513166502101</v>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="30">
         <v>0.75915050824021502</v>
       </c>
-      <c r="G44" s="25">
+      <c r="G44" s="30">
         <v>1.51023010747413</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="20" t="s">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="26">
         <v>13.828099999999999</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="27">
         <v>0.45993125581394501</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="27">
         <v>1.88492546748256</v>
       </c>
-      <c r="G45" s="22">
+      <c r="G45" s="27">
         <v>3.0087160259682402</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="23" t="s">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="24">
+      <c r="D46" s="29">
         <v>8.8483400000000004E-2</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="30">
         <v>0.50439958268898499</v>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="30">
         <v>1.17428808388124</v>
       </c>
-      <c r="G46" s="25">
+      <c r="G46" s="30">
         <v>1.8642873922166101</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="20" t="s">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="26">
         <v>1.0792299999999999</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="27">
         <v>0.23694535093489999</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="27">
         <v>0.75638934371671995</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="27">
         <v>1.51030932819276</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="29">
         <v>1.5731599999999999</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="30">
         <v>0.229718036094717</v>
       </c>
-      <c r="F48" s="25">
+      <c r="F48" s="30">
         <v>0.77961498364586002</v>
       </c>
-      <c r="G48" s="25">
+      <c r="G48" s="30">
         <v>1.4616668194278799</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49" s="20" t="s">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="21">
+      <c r="D49" s="26">
         <v>1.5713614</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="27">
         <v>0.40071241252664902</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="27">
         <v>0.96581405788355201</v>
       </c>
-      <c r="G49" s="22">
+      <c r="G49" s="27">
         <v>1.9214747959175</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="23" t="s">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D50" s="24">
+      <c r="D50" s="29">
         <v>6.6156800000000002</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="30">
         <v>0.14592883124204001</v>
       </c>
-      <c r="F50" s="25">
+      <c r="F50" s="30">
         <v>0.60449260703643604</v>
       </c>
-      <c r="G50" s="25">
+      <c r="G50" s="30">
         <v>1.0055006730877001</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51" s="20" t="s">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D51" s="21">
+      <c r="D51" s="26">
         <v>35.988700000000001</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E51" s="27">
         <v>0.12968113651434601</v>
       </c>
-      <c r="F51" s="22">
+      <c r="F51" s="27">
         <v>0.57749149831848201</v>
       </c>
-      <c r="G51" s="22">
+      <c r="G51" s="27">
         <v>1.0185314034547699</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="23" t="s">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D52" s="24">
+      <c r="D52" s="29">
         <v>0.292354</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="30">
         <v>0.31220361801305802</v>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="30">
         <v>0.73540788758055997</v>
       </c>
-      <c r="G52" s="25">
+      <c r="G52" s="30">
         <v>0.73616458940486895</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53" s="20" t="s">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="21">
+      <c r="D53" s="26">
         <v>13.1905</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E53" s="27">
         <v>3.3790369124594198E-3</v>
       </c>
-      <c r="F53" s="22">
+      <c r="F53" s="27">
         <v>1.0685154303572E-2</v>
       </c>
-      <c r="G53" s="22">
+      <c r="G53" s="27">
         <v>1.9292474326642099E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D54" s="24">
+      <c r="D54" s="29">
         <v>1.1140000000000001</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="30">
         <v>0.249127964789603</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="30">
         <v>0.88938504322949796</v>
       </c>
-      <c r="G54" s="25">
+      <c r="G54" s="30">
         <v>1.3298393318872299</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A55" s="20" t="s">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D55" s="21">
+      <c r="D55" s="26">
         <v>1.9451883000000001</v>
       </c>
-      <c r="E55" s="22">
+      <c r="E55" s="27">
         <v>0.40359911336578402</v>
       </c>
-      <c r="F55" s="22">
+      <c r="F55" s="27">
         <v>0.62498700848665001</v>
       </c>
-      <c r="G55" s="22">
+      <c r="G55" s="27">
         <v>1.1677899083337999</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="23" t="s">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D56" s="24">
+      <c r="D56" s="29">
         <v>9.6140600000000003</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="30">
         <v>9.8471561707902805E-2</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="30">
         <v>0.33753961371707603</v>
       </c>
-      <c r="G56" s="25">
+      <c r="G56" s="30">
         <v>0.61523698654407699</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57" s="20" t="s">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D57" s="21">
+      <c r="D57" s="26">
         <v>17.239699999999999</v>
       </c>
-      <c r="E57" s="22">
+      <c r="E57" s="27">
         <v>0.14224438082638899</v>
       </c>
-      <c r="F57" s="22">
+      <c r="F57" s="27">
         <v>0.414745195132116</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="27">
         <v>0.80134390579414105</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="23" t="s">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D58" s="24">
+      <c r="D58" s="29">
         <v>6.8042199999999997E-2</v>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="30">
         <v>0.50760907712574199</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="30">
         <v>1.09124651945925</v>
       </c>
-      <c r="G58" s="25">
+      <c r="G58" s="30">
         <v>1.10549516064681</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59" s="20" t="s">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="21">
+      <c r="D59" s="26">
         <v>3.1019899999999998</v>
       </c>
-      <c r="E59" s="22">
+      <c r="E59" s="27">
         <v>9.8036203584847603E-2</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="27">
         <v>0.30778567176863803</v>
       </c>
-      <c r="G59" s="22">
+      <c r="G59" s="27">
         <v>0.58570046607555803</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" s="23" t="s">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D60" s="24">
+      <c r="D60" s="29">
         <v>2.7850799999999998</v>
       </c>
-      <c r="E60" s="25">
+      <c r="E60" s="30">
         <v>9.71806155299062E-2</v>
       </c>
-      <c r="F60" s="25">
+      <c r="F60" s="30">
         <v>0.295448031130705</v>
       </c>
-      <c r="G60" s="25">
+      <c r="G60" s="30">
         <v>0.57115690156416798</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A61" s="20" t="s">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D61" s="21">
+      <c r="D61" s="26">
         <v>0.69017720000000005</v>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="27">
         <v>0.131432654739953</v>
       </c>
-      <c r="F61" s="22">
+      <c r="F61" s="27">
         <v>0.54299357139798299</v>
       </c>
-      <c r="G61" s="22">
+      <c r="G61" s="27">
         <v>1.0098621954920799</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="11" t="s">
         <v>37</v>
       </c>
       <c r="L62" t="s">
@@ -5594,7 +5659,7 @@
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="11" t="s">
         <v>36</v>
       </c>
       <c r="L63" t="s">
@@ -5602,7 +5667,7 @@
       </c>
     </row>
     <row r="65" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K65" s="7" t="s">
+      <c r="K65" s="11" t="s">
         <v>55</v>
       </c>
       <c r="L65" t="s">
@@ -5619,122 +5684,180 @@
       </c>
     </row>
     <row r="66" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K66" s="8" t="s">
+      <c r="K66" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="L66" s="11">
+      <c r="L66" s="15">
         <v>28.035107</v>
       </c>
-      <c r="M66" s="12">
+      <c r="M66" s="16">
         <v>0.13910073921247004</v>
       </c>
-      <c r="N66" s="12">
+      <c r="N66" s="16">
         <v>0.51048088727152119</v>
       </c>
-      <c r="O66" s="12">
+      <c r="O66" s="16">
         <v>0.94766945499370725</v>
       </c>
     </row>
     <row r="67" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K67" s="8" t="s">
+      <c r="K67" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="L67" s="11">
+      <c r="L67" s="15">
         <v>33.380251000000001</v>
       </c>
-      <c r="M67" s="12">
+      <c r="M67" s="16">
         <v>0.24633700319908547</v>
       </c>
-      <c r="N67" s="12">
+      <c r="N67" s="16">
         <v>0.98231866318178729</v>
       </c>
-      <c r="O67" s="12">
+      <c r="O67" s="16">
         <v>1.6136168321521187</v>
       </c>
     </row>
     <row r="68" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K68" s="8" t="s">
+      <c r="K68" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L68" s="11">
+      <c r="L68" s="15">
         <v>0.21431762000000001</v>
       </c>
-      <c r="M68" s="12">
+      <c r="M68" s="16">
         <v>0.41472425317527806</v>
       </c>
-      <c r="N68" s="12">
+      <c r="N68" s="16">
         <v>1.0467799336848513</v>
       </c>
-      <c r="O68" s="12">
+      <c r="O68" s="16">
         <v>1.429694802053032</v>
       </c>
     </row>
     <row r="69" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K69" s="8" t="s">
+      <c r="K69" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L69" s="15">
         <v>4.7895820000000002</v>
       </c>
-      <c r="M69" s="12">
+      <c r="M69" s="16">
         <v>0.12254273977925523</v>
       </c>
-      <c r="N69" s="12">
+      <c r="N69" s="16">
         <v>0.48889465777763313</v>
       </c>
-      <c r="O69" s="12">
+      <c r="O69" s="16">
         <v>0.90878341915603333</v>
       </c>
     </row>
     <row r="70" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K70" s="8" t="s">
+      <c r="K70" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="L70" s="11">
+      <c r="L70" s="15">
         <v>3.4851573</v>
       </c>
-      <c r="M70" s="12">
+      <c r="M70" s="16">
         <v>0.13494607028148947</v>
       </c>
-      <c r="N70" s="12">
+      <c r="N70" s="16">
         <v>0.50411365699925614</v>
       </c>
-      <c r="O70" s="12">
+      <c r="O70" s="16">
         <v>0.94189978729886814</v>
       </c>
     </row>
     <row r="71" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K71" s="8" t="s">
+      <c r="K71" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="L71" s="11">
+      <c r="L71" s="15">
         <v>2.3101450400000005</v>
       </c>
-      <c r="M71" s="12">
+      <c r="M71" s="16">
         <v>0.27788735892611011</v>
       </c>
-      <c r="N71" s="12">
+      <c r="N71" s="16">
         <v>0.97554330008965773</v>
       </c>
-      <c r="O71" s="12">
+      <c r="O71" s="16">
         <v>1.7714690063210139</v>
       </c>
     </row>
     <row r="72" spans="11:15" x14ac:dyDescent="0.35">
-      <c r="K72" s="8" t="s">
+      <c r="K72" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L72" s="11">
+      <c r="L72" s="15">
         <v>12.035759993333333</v>
       </c>
-      <c r="M72" s="10">
+      <c r="M72" s="14">
         <v>0.22258969409561474</v>
       </c>
-      <c r="N72" s="10">
+      <c r="N72" s="14">
         <v>0.75135518316745076</v>
       </c>
-      <c r="O72" s="10">
+      <c r="O72" s="14">
         <v>1.268855550329129</v>
+      </c>
+    </row>
+    <row r="79" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="M79" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="80" spans="11:15" x14ac:dyDescent="0.35">
+      <c r="M80" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="M81" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="M82" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N82" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="83" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="M83" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="M84" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="K88" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="K89" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="K90" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="K91" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="11:14" x14ac:dyDescent="0.35">
+      <c r="K92" s="18" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -5755,7 +5878,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B3" t="s">
@@ -5763,50 +5886,50 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="13">
         <v>29.022560999999996</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="13">
         <v>32.52543099999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="13">
         <v>0.21369023000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="13">
         <v>4.8820490000000003</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="13">
         <v>3.6192212999999995</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="13">
         <v>14.052590505999996</v>
       </c>
     </row>
@@ -5825,7 +5948,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B1" t="s">
@@ -5833,50 +5956,50 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="13">
         <v>20.114168810000002</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="13">
         <v>10.906844200000002</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="13">
         <v>15.12046445</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="13">
         <v>15.12046445</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="13">
         <v>9.0010106199999989</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="13">
         <v>14.052590506000001</v>
       </c>
     </row>
@@ -6944,7 +7067,7 @@
       <c r="C53" t="s">
         <v>64</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="14">
         <v>7.4497472269780495E-5</v>
       </c>
       <c r="E53">
@@ -6964,7 +7087,7 @@
       <c r="C54" t="s">
         <v>64</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="14">
         <v>8.0158078411725396E-5</v>
       </c>
       <c r="E54">
